--- a/user_input_format.xlsx
+++ b/user_input_format.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dcb543a2e6e05b1/Documents/Capstone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamis\Desktop\bv05-forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{5DAB21B5-C731-4053-A92F-88DD7CEE5A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA57BB7B-2C72-41F9-94C6-1B7E4C518B31}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" xr2:uid="{DA355075-E574-4132-8605-550514242227}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200"/>
   </bookViews>
   <sheets>
     <sheet name="User Input Data Template" sheetId="1" r:id="rId1"/>
@@ -127,8 +126,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,7 +279,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -460,14 +459,8 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -582,21 +575,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -642,20 +620,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -668,7 +637,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1049,40 +1024,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B38288-D5C4-4237-9AED-0B424627CD01}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.1640625" customWidth="1"/>
+    <col min="3" max="3" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B3">
+        <v>1.7</v>
+      </c>
+      <c r="C3">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B4">
+        <v>11.5</v>
+      </c>
+      <c r="C4">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B5">
+        <v>4.3</v>
+      </c>
+      <c r="C5">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B7">
+        <v>2.7</v>
+      </c>
+      <c r="C7">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B8">
+        <v>-0.8</v>
+      </c>
+      <c r="C8">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B9">
+        <v>0.1</v>
+      </c>
+      <c r="C9">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B10">
+        <v>4.3</v>
+      </c>
+      <c r="C10">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B11">
+        <v>11.9</v>
+      </c>
+      <c r="C11">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B13">
+        <v>6.1</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B14">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C14">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B15">
+        <v>14.5</v>
+      </c>
+      <c r="C15">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B16">
+        <v>3.4</v>
+      </c>
+      <c r="C16">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>11.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1090,185 +1226,185 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B94900-D4D9-4911-B12D-E0A6B31396D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4"/>
+      <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="10" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="6" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="10" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="6" t="s">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4"/>
+      <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="10" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="B13" t="s">
         <v>12</v>
       </c>

--- a/user_input_format.xlsx
+++ b/user_input_format.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamis\Desktop\bv05-forecast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dcb543a2e6e05b1/Documents/Capstone/load_forecasting/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{5DAB21B5-C731-4053-A92F-88DD7CEE5A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C7BFD84-5C0D-4365-9157-80E645337723}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DA355075-E574-4132-8605-550514242227}"/>
   </bookViews>
   <sheets>
     <sheet name="User Input Data Template" sheetId="1" r:id="rId1"/>
@@ -126,8 +127,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,7 +280,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,8 +460,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -575,6 +582,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -623,20 +645,22 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1024,200 +1048,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B38288-D5C4-4237-9AED-0B424627CD01}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.1640625" customWidth="1"/>
-    <col min="3" max="3" width="37.25" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46113</v>
       </c>
       <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46114</v>
       </c>
       <c r="B3">
-        <v>1.7</v>
+        <v>-12</v>
       </c>
       <c r="C3">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46115</v>
       </c>
       <c r="B4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46116</v>
       </c>
       <c r="B5">
-        <v>4.3</v>
+        <v>27</v>
       </c>
       <c r="C5">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46117</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="C6">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46118</v>
       </c>
       <c r="B7">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46119</v>
       </c>
       <c r="B8">
-        <v>-0.8</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>46120</v>
-      </c>
-      <c r="B9">
-        <v>0.1</v>
-      </c>
-      <c r="C9">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>46121</v>
-      </c>
-      <c r="B10">
-        <v>4.3</v>
-      </c>
-      <c r="C10">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B11">
-        <v>11.9</v>
-      </c>
-      <c r="C11">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1">
-        <v>46123</v>
-      </c>
-      <c r="B12">
         <v>9</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1">
-        <v>46124</v>
-      </c>
-      <c r="B13">
-        <v>6.1</v>
-      </c>
-      <c r="C13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
-        <v>46125</v>
-      </c>
-      <c r="B14">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C14">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1">
-        <v>46126</v>
-      </c>
-      <c r="B15">
-        <v>14.5</v>
-      </c>
-      <c r="C15">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1">
-        <v>46127</v>
-      </c>
-      <c r="B16">
-        <v>3.4</v>
-      </c>
-      <c r="C16">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1">
-        <v>46128</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>11.4</v>
       </c>
     </row>
   </sheetData>
@@ -1226,11 +1151,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B94900-D4D9-4911-B12D-E0A6B31396D6}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
@@ -1249,24 +1174,24 @@
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1285,7 +1210,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1294,117 +1219,90 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="4"/>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
       <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="F6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="2" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>12</v>
       </c>

--- a/user_input_format.xlsx
+++ b/user_input_format.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dcb543a2e6e05b1/Documents/Capstone/load_forecasting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\razah\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{5DAB21B5-C731-4053-A92F-88DD7CEE5A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C7BFD84-5C0D-4365-9157-80E645337723}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F64E6C-12F0-477A-A1AF-408200EDD8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DA355075-E574-4132-8605-550514242227}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{DA355075-E574-4132-8605-550514242227}"/>
   </bookViews>
   <sheets>
     <sheet name="User Input Data Template" sheetId="1" r:id="rId1"/>
     <sheet name="Read me" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -642,7 +655,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -660,6 +673,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -726,10 +742,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,15 +1061,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B38288-D5C4-4237-9AED-0B424627CD01}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.1796875" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1068,82 +1080,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>46113</v>
-      </c>
-      <c r="B2">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B3">
-        <v>-12</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46115</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46116</v>
-      </c>
-      <c r="B5">
-        <v>27</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B6">
-        <v>-7</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46119</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,28 +1176,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B94900-D4D9-4911-B12D-E0A6B31396D6}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1191,71 +1214,71 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
       <c r="F5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
       <c r="F6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
       <c r="F7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1272,7 +1295,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1289,7 +1312,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1297,12 +1320,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>12</v>
       </c>
